--- a/sample/サンプル入力.xlsx
+++ b/sample/サンプル入力.xlsx
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>佐藤蓮</t>
+          <t>佐藤陽翔</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>佐藤蓮</t>
+          <t>佐藤陽翔</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>鈴木凛</t>
+          <t>鈴木悠真</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>鈴木凛</t>
+          <t>鈴木悠真</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>鈴木凛</t>
+          <t>鈴木悠真</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>高橋海斗</t>
+          <t>高橋蓮</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>高橋海斗</t>
+          <t>高橋蓮</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>田中大和</t>
+          <t>田中凛</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>伊藤心春</t>
+          <t>伊藤海斗</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>伊藤心春</t>
+          <t>伊藤海斗</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>渡辺陽葵</t>
+          <t>渡辺大和</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>渡辺陽葵</t>
+          <t>渡辺大和</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>山本樹</t>
+          <t>山本心春</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>山本樹</t>
+          <t>山本心春</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>中村湊</t>
+          <t>中村陽葵</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>小林芽依</t>
+          <t>小林樹</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>小林芽依</t>
+          <t>小林樹</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>加藤葵</t>
+          <t>加藤湊</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>吉田颯太</t>
+          <t>吉田芽依</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>吉田颯太</t>
+          <t>吉田芽依</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>山田結衣</t>
+          <t>山田葵</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>松本美咲</t>
+          <t>松本颯太</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>井上陽翔</t>
+          <t>井上結衣</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>井上陽翔</t>
+          <t>井上結衣</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>木村悠真</t>
+          <t>木村美咲</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>木村悠真</t>
+          <t>木村美咲</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>佐藤蓮</t>
+          <t>佐藤陽翔</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>鈴木凛</t>
+          <t>鈴木悠真</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>高橋海斗</t>
+          <t>高橋蓮</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>田中大和</t>
+          <t>田中凛</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>伊藤心春</t>
+          <t>伊藤海斗</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>渡辺陽葵</t>
+          <t>渡辺大和</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>山本樹</t>
+          <t>山本心春</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>中村湊</t>
+          <t>中村陽葵</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -4300,7 +4300,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>小林芽依</t>
+          <t>小林樹</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>加藤葵</t>
+          <t>加藤湊</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>吉田颯太</t>
+          <t>吉田芽依</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>山田結衣</t>
+          <t>山田葵</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>松本美咲</t>
+          <t>松本颯太</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>井上陽翔</t>
+          <t>井上結衣</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -4708,7 +4708,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>木村悠真</t>
+          <t>木村美咲</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>

--- a/sample/サンプル入力.xlsx
+++ b/sample/サンプル入力.xlsx
@@ -448,7 +448,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:30</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>19:00</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
     </row>
@@ -493,7 +493,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>22:00</t>
         </is>
       </c>
     </row>
